--- a/public/refractive-outcomes-analyzer/blank-data-sheet-template.xlsx
+++ b/public/refractive-outcomes-analyzer/blank-data-sheet-template.xlsx
@@ -780,7 +780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH421"/>
+  <dimension ref="A1:AJ421"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -957,6 +957,11 @@
       <c r="AF3" s="53" t="n"/>
       <c r="AG3" s="53" t="n"/>
       <c r="AH3" s="53" t="n"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>PRE-OP VISION (optional — unlocks standard graphs)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="33.75" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -1129,6 +1134,16 @@
           <t>Post_K_Steep_Axis_deg</t>
         </is>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Pre_UDVA_logMAR</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Pre_CDVA_logMAR</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="33.75" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
@@ -1299,6 +1314,16 @@
       <c r="AH5" s="8" t="inlineStr">
         <is>
           <t>Axis of the post-op steep meridian (°)</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Pre-op uncorrected VA (logMAR, Snellen 6/60 or 20/200, or decimal)</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Pre-op best-corrected VA — enables efficacy &amp; safety indices, UDVA-vs-CDVA and lines-gained/lost graphs</t>
         </is>
       </c>
     </row>
